--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:40+00:00</t>
+    <t>2026-04-20T06:44:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4952,7 +4952,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>167</v>
       </c>
@@ -4971,7 +4971,7 @@
         <v>75</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>74</v>
@@ -10604,7 +10604,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
         <v>281</v>
       </c>
@@ -10623,7 +10623,7 @@
         <v>75</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>74</v>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T06:44:24+00:00</t>
+    <t>2026-04-20T07:29:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:29:37+00:00</t>
+    <t>2026-04-20T13:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
